--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F492"/>
+  <dimension ref="A1:F497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12356,6 +12356,146 @@
       </c>
       <c r="F492" t="inlineStr"/>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>13-D-6195-01-(12Ga Galv) - K30 - V1-R0</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>12 Galv</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Length: 35.75 * Width: 2.5</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>13-D-6196-01</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>13-D-6196-01-(12Ga Galv) - K30 - V2-R0</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>12 Galv</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Length: 35.75 * Width: 2.5</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>P20153S-04</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>P20153S-04-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>14 Galv</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Length: 7.37 * Width: 1.53</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>P20321S-05</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>P20321S-05-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>14 Galv</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Length: 5.69 * Width: 2.84</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>P20321S-06</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>P20321S-06-(14Ga Galv) - K30 - V0-R0</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>14 Galv</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Length: 36.25 * Width: 2.38</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Galv</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -12379,7 +12379,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Galv</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -12313,7 +12313,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>14 Galv</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>14 Galv</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>12 Galv</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>12 Galv</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -12425,7 +12425,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>14 Galv</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>14 Galv</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>14 Galv</t>
+          <t>14GA</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -12541,7 +12541,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>12GALV</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>GALV</t>
+          <t>Galvanizado</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>12GALV</t>
+          <t>12GA</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>GALV</t>
+          <t>Galvanizado</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>14Gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>14Gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>12Gacr</t>
+          <t>12GACR</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>14Gacr</t>
+          <t>14GACR</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>ANSI61</t>
+          <t>Ansi 61</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F504"/>
+  <dimension ref="A1:F505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12744,6 +12744,30 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>12-D-6106-01</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>12-D-6106-01</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr"/>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>12-D-6106-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="1339">
   <si>
     <t>SKU</t>
   </si>
@@ -1603,6 +1603,12 @@
     <t>11-C-9778-01 TRT0</t>
   </si>
   <si>
+    <t>12-D-6030-07</t>
+  </si>
+  <si>
+    <t>12-D-6030-08</t>
+  </si>
+  <si>
     <t>11-6463-01-(12gacr ANSI-61) - K61 - V6-R0</t>
   </si>
   <si>
@@ -1741,6 +1747,9 @@
     <t>12-D-6017-02-(10Ga Galv) - K30 - V1-R0</t>
   </si>
   <si>
+    <t>12-D-6030-10 - PLATE TOP GALVANIZADO</t>
+  </si>
+  <si>
     <t>12-D-6033-05-(12gacr ANSI-61) - K48 - V2-R0</t>
   </si>
   <si>
@@ -2234,6 +2243,12 @@
   </si>
   <si>
     <t>11-C-9778-01 TRT0 - Proyecto TORONTO</t>
+  </si>
+  <si>
+    <t>12-D-6030-07 - PLATE TOP GALVANIZADO</t>
+  </si>
+  <si>
+    <t>12-D-6030-08 - PLATE TOP GALVANIZADO</t>
   </si>
   <si>
     <t>12GACR</t>
@@ -4347,7 +4362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F524"/>
+  <dimension ref="A1:F526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4375,16 +4390,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C2" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="E2" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -4395,19 +4410,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C3" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D3" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E3" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F3" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4415,19 +4430,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C4" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D4" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="E4" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F4" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4435,19 +4450,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C5" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D5" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="E5" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F5" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4455,16 +4470,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C6" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D6" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="E6" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -4475,19 +4490,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C7" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D7" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="E7" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F7" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4495,10 +4510,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F8" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4506,10 +4521,10 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F9" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4517,19 +4532,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C10" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D10" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E10" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F10" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4537,19 +4552,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C11" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D11" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="E11" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F11" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4557,19 +4572,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C12" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D12" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="E12" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F12" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4577,16 +4592,16 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C13" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E13" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F13" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4594,16 +4609,16 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C14" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E14" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F14" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4611,10 +4626,10 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F15" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4622,10 +4637,10 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F16" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4633,10 +4648,10 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F17" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4644,10 +4659,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F18" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4655,10 +4670,10 @@
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F19" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4666,10 +4681,10 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F20" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4677,10 +4692,10 @@
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F21" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4688,10 +4703,10 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F22" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4699,10 +4714,10 @@
         <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F23" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4710,10 +4725,10 @@
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F24" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4721,10 +4736,10 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F25" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4732,10 +4747,10 @@
         <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F26" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4743,10 +4758,10 @@
         <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F27" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4754,10 +4769,10 @@
         <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F28" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4765,10 +4780,10 @@
         <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F29" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4776,10 +4791,10 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F30" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4787,10 +4802,10 @@
         <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F31" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4798,10 +4813,10 @@
         <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F32" t="s">
-        <v>911</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4809,10 +4824,10 @@
         <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F33" t="s">
-        <v>912</v>
+        <v>917</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4820,10 +4835,10 @@
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F34" t="s">
-        <v>913</v>
+        <v>918</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4831,10 +4846,10 @@
         <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F35" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4842,10 +4857,10 @@
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F36" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4853,10 +4868,10 @@
         <v>41</v>
       </c>
       <c r="E37" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F37" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4864,10 +4879,10 @@
         <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F38" t="s">
-        <v>917</v>
+        <v>922</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4875,10 +4890,10 @@
         <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F39" t="s">
-        <v>918</v>
+        <v>923</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4886,10 +4901,10 @@
         <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F40" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4897,10 +4912,10 @@
         <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F41" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4908,10 +4923,10 @@
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F42" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4919,10 +4934,10 @@
         <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F43" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4930,10 +4945,10 @@
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F44" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4941,10 +4956,10 @@
         <v>49</v>
       </c>
       <c r="E45" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F45" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4952,10 +4967,10 @@
         <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F46" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4963,10 +4978,10 @@
         <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F47" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4974,10 +4989,10 @@
         <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F48" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4985,10 +5000,10 @@
         <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F49" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4996,10 +5011,10 @@
         <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F50" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5007,10 +5022,10 @@
         <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F51" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5018,10 +5033,10 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F52" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5029,10 +5044,10 @@
         <v>57</v>
       </c>
       <c r="E53" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F53" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5040,10 +5055,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F54" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5051,10 +5066,10 @@
         <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F55" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -5062,13 +5077,13 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E56" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F56" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5076,13 +5091,13 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E57" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F57" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5090,10 +5105,10 @@
         <v>62</v>
       </c>
       <c r="E58" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F58" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -5101,10 +5116,10 @@
         <v>63</v>
       </c>
       <c r="E59" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F59" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -5112,10 +5127,10 @@
         <v>64</v>
       </c>
       <c r="E60" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F60" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -5123,10 +5138,10 @@
         <v>65</v>
       </c>
       <c r="E61" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F61" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5134,10 +5149,10 @@
         <v>66</v>
       </c>
       <c r="E62" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F62" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5145,10 +5160,10 @@
         <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F63" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5156,10 +5171,10 @@
         <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F64" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5167,10 +5182,10 @@
         <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F65" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5178,10 +5193,10 @@
         <v>70</v>
       </c>
       <c r="E66" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F66" t="s">
-        <v>945</v>
+        <v>950</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5189,19 +5204,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C67" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D67" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="E67" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F67" t="s">
-        <v>946</v>
+        <v>951</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5209,10 +5224,10 @@
         <v>72</v>
       </c>
       <c r="E68" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F68" t="s">
-        <v>947</v>
+        <v>952</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5220,10 +5235,10 @@
         <v>73</v>
       </c>
       <c r="E69" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F69" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5231,10 +5246,10 @@
         <v>74</v>
       </c>
       <c r="E70" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F70" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -5242,10 +5257,10 @@
         <v>75</v>
       </c>
       <c r="E71" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F71" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5253,10 +5268,10 @@
         <v>76</v>
       </c>
       <c r="E72" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F72" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -5264,10 +5279,10 @@
         <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F73" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5275,10 +5290,10 @@
         <v>78</v>
       </c>
       <c r="E74" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F74" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5286,10 +5301,10 @@
         <v>79</v>
       </c>
       <c r="E75" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F75" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5297,13 +5312,13 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E76" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F76" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5311,13 +5326,13 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E77" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F77" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5325,10 +5340,10 @@
         <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F78" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5336,10 +5351,10 @@
         <v>83</v>
       </c>
       <c r="E79" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F79" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5347,10 +5362,10 @@
         <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F80" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5358,10 +5373,10 @@
         <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F81" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5369,10 +5384,10 @@
         <v>86</v>
       </c>
       <c r="E82" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F82" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5380,10 +5395,10 @@
         <v>87</v>
       </c>
       <c r="E83" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F83" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5391,10 +5406,10 @@
         <v>88</v>
       </c>
       <c r="E84" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F84" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5402,10 +5417,10 @@
         <v>89</v>
       </c>
       <c r="E85" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F85" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5413,10 +5428,10 @@
         <v>90</v>
       </c>
       <c r="E86" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F86" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5424,10 +5439,10 @@
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F87" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5435,10 +5450,10 @@
         <v>92</v>
       </c>
       <c r="E88" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F88" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5446,10 +5461,10 @@
         <v>93</v>
       </c>
       <c r="E89" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F89" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5457,10 +5472,10 @@
         <v>94</v>
       </c>
       <c r="E90" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F90" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5468,10 +5483,10 @@
         <v>95</v>
       </c>
       <c r="E91" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F91" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5479,10 +5494,10 @@
         <v>96</v>
       </c>
       <c r="E92" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F92" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5490,10 +5505,10 @@
         <v>97</v>
       </c>
       <c r="E93" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F93" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5501,10 +5516,10 @@
         <v>98</v>
       </c>
       <c r="E94" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F94" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5512,10 +5527,10 @@
         <v>99</v>
       </c>
       <c r="E95" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F95" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -5523,10 +5538,10 @@
         <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F96" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -5534,10 +5549,10 @@
         <v>101</v>
       </c>
       <c r="E97" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F97" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -5545,10 +5560,10 @@
         <v>102</v>
       </c>
       <c r="E98" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F98" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -5556,10 +5571,10 @@
         <v>103</v>
       </c>
       <c r="E99" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F99" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -5567,10 +5582,10 @@
         <v>104</v>
       </c>
       <c r="E100" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F100" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -5578,10 +5593,10 @@
         <v>105</v>
       </c>
       <c r="E101" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F101" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5589,10 +5604,10 @@
         <v>106</v>
       </c>
       <c r="E102" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F102" t="s">
-        <v>981</v>
+        <v>986</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -5600,16 +5615,16 @@
         <v>107</v>
       </c>
       <c r="B103" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C103" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D103" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E103" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F103" t="s">
         <v>107</v>
@@ -5620,10 +5635,10 @@
         <v>108</v>
       </c>
       <c r="E104" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F104" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -5631,10 +5646,10 @@
         <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F105" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -5642,10 +5657,10 @@
         <v>110</v>
       </c>
       <c r="E106" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F106" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -5653,10 +5668,10 @@
         <v>111</v>
       </c>
       <c r="E107" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F107" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -5664,10 +5679,10 @@
         <v>112</v>
       </c>
       <c r="E108" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F108" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -5675,10 +5690,10 @@
         <v>113</v>
       </c>
       <c r="E109" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F109" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -5686,10 +5701,10 @@
         <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F110" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -5697,10 +5712,10 @@
         <v>115</v>
       </c>
       <c r="E111" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F111" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -5708,13 +5723,13 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E112" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F112" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5722,13 +5737,13 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E113" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F113" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5736,13 +5751,13 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E114" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F114" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5750,13 +5765,13 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E115" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F115" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5764,10 +5779,10 @@
         <v>120</v>
       </c>
       <c r="E116" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F116" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5775,13 +5790,13 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E117" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F117" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5789,10 +5804,10 @@
         <v>122</v>
       </c>
       <c r="E118" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F118" t="s">
-        <v>996</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5800,10 +5815,10 @@
         <v>123</v>
       </c>
       <c r="E119" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F119" t="s">
-        <v>997</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5811,13 +5826,13 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E120" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F120" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5825,13 +5840,13 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E121" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F121" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5839,10 +5854,10 @@
         <v>126</v>
       </c>
       <c r="E122" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F122" t="s">
-        <v>1000</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5850,10 +5865,10 @@
         <v>127</v>
       </c>
       <c r="E123" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F123" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5861,10 +5876,10 @@
         <v>128</v>
       </c>
       <c r="E124" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F124" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5872,10 +5887,10 @@
         <v>129</v>
       </c>
       <c r="E125" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F125" t="s">
-        <v>1003</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5883,10 +5898,10 @@
         <v>130</v>
       </c>
       <c r="E126" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F126" t="s">
-        <v>1004</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5894,10 +5909,10 @@
         <v>131</v>
       </c>
       <c r="E127" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F127" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5905,10 +5920,10 @@
         <v>132</v>
       </c>
       <c r="E128" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F128" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5916,10 +5931,10 @@
         <v>133</v>
       </c>
       <c r="E129" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F129" t="s">
-        <v>1007</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5927,10 +5942,10 @@
         <v>134</v>
       </c>
       <c r="E130" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F130" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5938,13 +5953,13 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E131" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F131" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5952,13 +5967,13 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E132" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F132" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5966,13 +5981,13 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E133" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F133" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -5980,13 +5995,13 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E134" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F134" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -5994,10 +6009,10 @@
         <v>139</v>
       </c>
       <c r="E135" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F135" t="s">
-        <v>1013</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6005,10 +6020,10 @@
         <v>140</v>
       </c>
       <c r="E136" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F136" t="s">
-        <v>1014</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -6016,13 +6031,13 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E137" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F137" t="s">
-        <v>1015</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6030,13 +6045,13 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E138" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F138" t="s">
-        <v>1016</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -6044,13 +6059,13 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E139" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F139" t="s">
-        <v>1017</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6058,13 +6073,13 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E140" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F140" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6072,10 +6087,10 @@
         <v>145</v>
       </c>
       <c r="E141" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F141" t="s">
-        <v>1019</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6083,10 +6098,10 @@
         <v>146</v>
       </c>
       <c r="E142" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F142" t="s">
-        <v>1020</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6094,13 +6109,13 @@
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E143" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F143" t="s">
-        <v>1021</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6108,13 +6123,13 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E144" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F144" t="s">
-        <v>1022</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -6122,13 +6137,13 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E145" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F145" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -6136,13 +6151,13 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E146" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F146" t="s">
-        <v>1024</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -6150,10 +6165,10 @@
         <v>151</v>
       </c>
       <c r="E147" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F147" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -6161,10 +6176,10 @@
         <v>152</v>
       </c>
       <c r="E148" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F148" t="s">
-        <v>1026</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -6172,13 +6187,13 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E149" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F149" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -6186,13 +6201,13 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E150" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F150" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -6200,13 +6215,13 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E151" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F151" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -6214,10 +6229,10 @@
         <v>156</v>
       </c>
       <c r="E152" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F152" t="s">
-        <v>1030</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -6225,10 +6240,10 @@
         <v>157</v>
       </c>
       <c r="E153" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F153" t="s">
-        <v>1031</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -6236,10 +6251,10 @@
         <v>158</v>
       </c>
       <c r="E154" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F154" t="s">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -6247,10 +6262,10 @@
         <v>159</v>
       </c>
       <c r="E155" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F155" t="s">
-        <v>1033</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -6258,10 +6273,10 @@
         <v>160</v>
       </c>
       <c r="E156" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F156" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -6269,10 +6284,10 @@
         <v>161</v>
       </c>
       <c r="E157" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F157" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -6280,10 +6295,10 @@
         <v>162</v>
       </c>
       <c r="E158" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F158" t="s">
-        <v>1036</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -6291,10 +6306,10 @@
         <v>163</v>
       </c>
       <c r="E159" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F159" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -6302,10 +6317,10 @@
         <v>164</v>
       </c>
       <c r="E160" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F160" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -6313,13 +6328,13 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E161" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F161" t="s">
-        <v>1039</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -6327,13 +6342,13 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E162" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F162" t="s">
-        <v>1040</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -6341,13 +6356,13 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E163" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F163" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -6355,10 +6370,10 @@
         <v>168</v>
       </c>
       <c r="E164" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F164" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -6366,10 +6381,10 @@
         <v>169</v>
       </c>
       <c r="E165" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F165" t="s">
-        <v>1043</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -6377,13 +6392,13 @@
         <v>170</v>
       </c>
       <c r="B166" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E166" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F166" t="s">
-        <v>1044</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -6391,19 +6406,19 @@
         <v>171</v>
       </c>
       <c r="B167" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C167" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D167" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="E167" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F167" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -6411,19 +6426,19 @@
         <v>172</v>
       </c>
       <c r="B168" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C168" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D168" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="E168" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F168" t="s">
-        <v>1046</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -6431,16 +6446,16 @@
         <v>173</v>
       </c>
       <c r="B169" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C169" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D169" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="E169" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F169" t="s">
         <v>173</v>
@@ -6451,16 +6466,16 @@
         <v>174</v>
       </c>
       <c r="B170" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C170" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E170" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F170" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -6468,16 +6483,16 @@
         <v>175</v>
       </c>
       <c r="B171" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C171" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D171" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E171" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F171" t="s">
         <v>175</v>
@@ -6488,16 +6503,16 @@
         <v>176</v>
       </c>
       <c r="B172" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C172" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D172" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="E172" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F172" t="s">
         <v>176</v>
@@ -6508,10 +6523,10 @@
         <v>177</v>
       </c>
       <c r="E173" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F173" t="s">
-        <v>1048</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -6519,10 +6534,10 @@
         <v>178</v>
       </c>
       <c r="E174" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F174" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -6530,10 +6545,10 @@
         <v>179</v>
       </c>
       <c r="E175" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F175" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -6541,10 +6556,10 @@
         <v>180</v>
       </c>
       <c r="E176" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F176" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6552,10 +6567,10 @@
         <v>181</v>
       </c>
       <c r="E177" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F177" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -6563,10 +6578,10 @@
         <v>182</v>
       </c>
       <c r="E178" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F178" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -6574,10 +6589,10 @@
         <v>183</v>
       </c>
       <c r="E179" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F179" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6585,10 +6600,10 @@
         <v>184</v>
       </c>
       <c r="E180" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F180" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -6596,10 +6611,10 @@
         <v>185</v>
       </c>
       <c r="E181" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F181" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -6607,10 +6622,10 @@
         <v>186</v>
       </c>
       <c r="E182" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F182" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6618,10 +6633,10 @@
         <v>187</v>
       </c>
       <c r="E183" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F183" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6629,10 +6644,10 @@
         <v>188</v>
       </c>
       <c r="E184" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F184" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -6640,10 +6655,10 @@
         <v>189</v>
       </c>
       <c r="E185" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F185" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -6651,10 +6666,10 @@
         <v>190</v>
       </c>
       <c r="E186" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F186" t="s">
-        <v>1061</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -6662,10 +6677,10 @@
         <v>191</v>
       </c>
       <c r="E187" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F187" t="s">
-        <v>1062</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6673,10 +6688,10 @@
         <v>192</v>
       </c>
       <c r="E188" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F188" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6684,10 +6699,10 @@
         <v>193</v>
       </c>
       <c r="E189" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F189" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6695,10 +6710,10 @@
         <v>194</v>
       </c>
       <c r="E190" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F190" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -6706,10 +6721,10 @@
         <v>195</v>
       </c>
       <c r="E191" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F191" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -6717,10 +6732,10 @@
         <v>196</v>
       </c>
       <c r="E192" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F192" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -6728,10 +6743,10 @@
         <v>197</v>
       </c>
       <c r="E193" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F193" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -6739,10 +6754,10 @@
         <v>198</v>
       </c>
       <c r="E194" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F194" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -6750,10 +6765,10 @@
         <v>199</v>
       </c>
       <c r="E195" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F195" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -6761,10 +6776,10 @@
         <v>200</v>
       </c>
       <c r="E196" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F196" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6772,10 +6787,10 @@
         <v>201</v>
       </c>
       <c r="E197" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F197" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -6783,10 +6798,10 @@
         <v>202</v>
       </c>
       <c r="E198" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F198" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -6794,10 +6809,10 @@
         <v>203</v>
       </c>
       <c r="E199" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F199" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -6805,10 +6820,10 @@
         <v>204</v>
       </c>
       <c r="E200" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F200" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -6816,10 +6831,10 @@
         <v>205</v>
       </c>
       <c r="E201" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F201" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -6827,10 +6842,10 @@
         <v>206</v>
       </c>
       <c r="E202" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F202" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -6838,10 +6853,10 @@
         <v>207</v>
       </c>
       <c r="E203" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F203" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -6849,10 +6864,10 @@
         <v>208</v>
       </c>
       <c r="E204" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F204" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -6860,10 +6875,10 @@
         <v>209</v>
       </c>
       <c r="E205" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F205" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -6871,10 +6886,10 @@
         <v>210</v>
       </c>
       <c r="E206" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F206" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -6882,10 +6897,10 @@
         <v>211</v>
       </c>
       <c r="E207" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F207" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -6893,10 +6908,10 @@
         <v>212</v>
       </c>
       <c r="E208" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F208" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -6904,10 +6919,10 @@
         <v>213</v>
       </c>
       <c r="E209" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F209" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -6915,10 +6930,10 @@
         <v>214</v>
       </c>
       <c r="E210" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F210" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -6926,10 +6941,10 @@
         <v>215</v>
       </c>
       <c r="E211" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F211" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -6937,10 +6952,10 @@
         <v>216</v>
       </c>
       <c r="E212" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F212" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -6948,10 +6963,10 @@
         <v>217</v>
       </c>
       <c r="E213" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F213" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -6959,10 +6974,10 @@
         <v>218</v>
       </c>
       <c r="E214" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F214" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6970,10 +6985,10 @@
         <v>219</v>
       </c>
       <c r="E215" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F215" t="s">
-        <v>1090</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6981,10 +6996,10 @@
         <v>220</v>
       </c>
       <c r="E216" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F216" t="s">
-        <v>1091</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6992,10 +7007,10 @@
         <v>221</v>
       </c>
       <c r="E217" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F217" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -7003,10 +7018,10 @@
         <v>222</v>
       </c>
       <c r="E218" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F218" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -7014,10 +7029,10 @@
         <v>223</v>
       </c>
       <c r="E219" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F219" t="s">
-        <v>1094</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -7025,10 +7040,10 @@
         <v>224</v>
       </c>
       <c r="E220" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F220" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7036,10 +7051,10 @@
         <v>225</v>
       </c>
       <c r="E221" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F221" t="s">
-        <v>1096</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -7047,10 +7062,10 @@
         <v>226</v>
       </c>
       <c r="E222" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F222" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -7058,10 +7073,10 @@
         <v>227</v>
       </c>
       <c r="E223" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F223" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7069,10 +7084,10 @@
         <v>228</v>
       </c>
       <c r="E224" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F224" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -7080,10 +7095,10 @@
         <v>229</v>
       </c>
       <c r="E225" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F225" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -7091,10 +7106,10 @@
         <v>230</v>
       </c>
       <c r="E226" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F226" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -7102,10 +7117,10 @@
         <v>231</v>
       </c>
       <c r="E227" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F227" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -7113,10 +7128,10 @@
         <v>232</v>
       </c>
       <c r="E228" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F228" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -7124,10 +7139,10 @@
         <v>233</v>
       </c>
       <c r="E229" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F229" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -7135,10 +7150,10 @@
         <v>234</v>
       </c>
       <c r="E230" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F230" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -7146,10 +7161,10 @@
         <v>235</v>
       </c>
       <c r="E231" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F231" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -7157,10 +7172,10 @@
         <v>236</v>
       </c>
       <c r="E232" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F232" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -7168,10 +7183,10 @@
         <v>237</v>
       </c>
       <c r="E233" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F233" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -7179,10 +7194,10 @@
         <v>238</v>
       </c>
       <c r="E234" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F234" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -7190,10 +7205,10 @@
         <v>239</v>
       </c>
       <c r="E235" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F235" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -7201,10 +7216,10 @@
         <v>240</v>
       </c>
       <c r="E236" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F236" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -7212,10 +7227,10 @@
         <v>241</v>
       </c>
       <c r="E237" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F237" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -7223,10 +7238,10 @@
         <v>242</v>
       </c>
       <c r="E238" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F238" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -7234,10 +7249,10 @@
         <v>243</v>
       </c>
       <c r="E239" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F239" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -7245,10 +7260,10 @@
         <v>244</v>
       </c>
       <c r="E240" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F240" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -7256,10 +7271,10 @@
         <v>245</v>
       </c>
       <c r="E241" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F241" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -7267,10 +7282,10 @@
         <v>246</v>
       </c>
       <c r="E242" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F242" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -7278,10 +7293,10 @@
         <v>247</v>
       </c>
       <c r="E243" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F243" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -7289,10 +7304,10 @@
         <v>248</v>
       </c>
       <c r="E244" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F244" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -7300,10 +7315,10 @@
         <v>249</v>
       </c>
       <c r="E245" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F245" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -7311,10 +7326,10 @@
         <v>250</v>
       </c>
       <c r="E246" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F246" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -7322,10 +7337,10 @@
         <v>251</v>
       </c>
       <c r="E247" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F247" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -7333,10 +7348,10 @@
         <v>252</v>
       </c>
       <c r="E248" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F248" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -7344,10 +7359,10 @@
         <v>253</v>
       </c>
       <c r="E249" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F249" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -7355,10 +7370,10 @@
         <v>254</v>
       </c>
       <c r="E250" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F250" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -7366,10 +7381,10 @@
         <v>255</v>
       </c>
       <c r="E251" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F251" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -7377,10 +7392,10 @@
         <v>256</v>
       </c>
       <c r="E252" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F252" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -7388,10 +7403,10 @@
         <v>257</v>
       </c>
       <c r="E253" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F253" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -7399,7 +7414,7 @@
         <v>258</v>
       </c>
       <c r="E254" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F254" t="s">
         <v>258</v>
@@ -7410,10 +7425,10 @@
         <v>259</v>
       </c>
       <c r="E255" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F255" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -7421,10 +7436,10 @@
         <v>260</v>
       </c>
       <c r="E256" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F256" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7432,10 +7447,10 @@
         <v>261</v>
       </c>
       <c r="E257" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F257" t="s">
-        <v>1131</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7443,10 +7458,10 @@
         <v>262</v>
       </c>
       <c r="E258" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F258" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7454,10 +7469,10 @@
         <v>263</v>
       </c>
       <c r="E259" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F259" t="s">
-        <v>1133</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7465,10 +7480,10 @@
         <v>264</v>
       </c>
       <c r="E260" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F260" t="s">
-        <v>1134</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7476,10 +7491,10 @@
         <v>265</v>
       </c>
       <c r="E261" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F261" t="s">
-        <v>1135</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7487,10 +7502,10 @@
         <v>266</v>
       </c>
       <c r="E262" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F262" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -7498,10 +7513,10 @@
         <v>267</v>
       </c>
       <c r="E263" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F263" t="s">
-        <v>1137</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7509,10 +7524,10 @@
         <v>268</v>
       </c>
       <c r="E264" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F264" t="s">
-        <v>1138</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7520,10 +7535,10 @@
         <v>269</v>
       </c>
       <c r="E265" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F265" t="s">
-        <v>1139</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7531,10 +7546,10 @@
         <v>270</v>
       </c>
       <c r="E266" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F266" t="s">
-        <v>1140</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7542,10 +7557,10 @@
         <v>271</v>
       </c>
       <c r="E267" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F267" t="s">
-        <v>1141</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7553,10 +7568,10 @@
         <v>272</v>
       </c>
       <c r="E268" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F268" t="s">
-        <v>1142</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7564,10 +7579,10 @@
         <v>273</v>
       </c>
       <c r="E269" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F269" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7575,10 +7590,10 @@
         <v>274</v>
       </c>
       <c r="E270" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F270" t="s">
-        <v>1144</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7586,10 +7601,10 @@
         <v>275</v>
       </c>
       <c r="E271" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F271" t="s">
-        <v>1145</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7597,10 +7612,10 @@
         <v>276</v>
       </c>
       <c r="E272" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F272" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7608,10 +7623,10 @@
         <v>277</v>
       </c>
       <c r="E273" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F273" t="s">
-        <v>1147</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7619,10 +7634,10 @@
         <v>278</v>
       </c>
       <c r="E274" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F274" t="s">
-        <v>1148</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7630,10 +7645,10 @@
         <v>279</v>
       </c>
       <c r="E275" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F275" t="s">
-        <v>1149</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7641,10 +7656,10 @@
         <v>280</v>
       </c>
       <c r="E276" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F276" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7652,10 +7667,10 @@
         <v>281</v>
       </c>
       <c r="E277" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F277" t="s">
-        <v>1151</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7663,10 +7678,10 @@
         <v>282</v>
       </c>
       <c r="E278" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F278" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7674,10 +7689,10 @@
         <v>283</v>
       </c>
       <c r="E279" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F279" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7685,10 +7700,10 @@
         <v>284</v>
       </c>
       <c r="E280" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F280" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7696,10 +7711,10 @@
         <v>285</v>
       </c>
       <c r="E281" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F281" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7707,10 +7722,10 @@
         <v>286</v>
       </c>
       <c r="E282" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F282" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7718,10 +7733,10 @@
         <v>287</v>
       </c>
       <c r="E283" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F283" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7729,16 +7744,16 @@
         <v>288</v>
       </c>
       <c r="B284" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C284" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D284" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="E284" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F284" t="s">
         <v>288</v>
@@ -7749,19 +7764,19 @@
         <v>289</v>
       </c>
       <c r="B285" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C285" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D285" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="E285" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F285" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7769,16 +7784,16 @@
         <v>290</v>
       </c>
       <c r="B286" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C286" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D286" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="E286" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F286" t="s">
         <v>290</v>
@@ -7789,19 +7804,19 @@
         <v>291</v>
       </c>
       <c r="B287" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C287" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D287" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E287" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F287" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7809,19 +7824,19 @@
         <v>292</v>
       </c>
       <c r="B288" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C288" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D288" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="E288" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F288" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7829,10 +7844,10 @@
         <v>293</v>
       </c>
       <c r="E289" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F289" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7840,16 +7855,16 @@
         <v>294</v>
       </c>
       <c r="B290" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C290" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D290" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="E290" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F290" t="s">
         <v>294</v>
@@ -7860,16 +7875,16 @@
         <v>295</v>
       </c>
       <c r="B291" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C291" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D291" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="E291" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F291" t="s">
         <v>295</v>
@@ -7880,10 +7895,10 @@
         <v>296</v>
       </c>
       <c r="E292" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F292" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -7891,16 +7906,16 @@
         <v>297</v>
       </c>
       <c r="B293" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C293" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D293" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="E293" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F293" t="s">
         <v>297</v>
@@ -7911,16 +7926,16 @@
         <v>298</v>
       </c>
       <c r="B294" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C294" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E294" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F294" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -7928,16 +7943,16 @@
         <v>299</v>
       </c>
       <c r="B295" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C295" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E295" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F295" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7945,19 +7960,19 @@
         <v>300</v>
       </c>
       <c r="B296" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C296" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D296" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="E296" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F296" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -7965,19 +7980,19 @@
         <v>301</v>
       </c>
       <c r="B297" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C297" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D297" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E297" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F297" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7985,10 +8000,10 @@
         <v>302</v>
       </c>
       <c r="E298" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F298" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -7996,16 +8011,16 @@
         <v>303</v>
       </c>
       <c r="B299" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C299" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E299" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F299" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -8013,13 +8028,13 @@
         <v>304</v>
       </c>
       <c r="B300" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E300" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F300" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -8027,19 +8042,19 @@
         <v>305</v>
       </c>
       <c r="B301" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C301" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D301" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="E301" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F301" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -8047,16 +8062,16 @@
         <v>306</v>
       </c>
       <c r="B302" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C302" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D302" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="E302" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F302" t="s">
         <v>306</v>
@@ -8067,19 +8082,19 @@
         <v>307</v>
       </c>
       <c r="B303" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C303" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D303" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="E303" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F303" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -8087,10 +8102,10 @@
         <v>308</v>
       </c>
       <c r="E304" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F304" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -8098,16 +8113,16 @@
         <v>309</v>
       </c>
       <c r="B305" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C305" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D305" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E305" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F305" t="s">
         <v>309</v>
@@ -8118,16 +8133,16 @@
         <v>310</v>
       </c>
       <c r="B306" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C306" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D306" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="E306" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F306" t="s">
         <v>310</v>
@@ -8138,19 +8153,19 @@
         <v>311</v>
       </c>
       <c r="B307" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C307" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D307" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="E307" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F307" t="s">
-        <v>1173</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -8158,16 +8173,16 @@
         <v>312</v>
       </c>
       <c r="B308" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C308" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D308" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E308" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F308" t="s">
         <v>312</v>
@@ -8178,19 +8193,19 @@
         <v>313</v>
       </c>
       <c r="B309" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C309" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D309" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="E309" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F309" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -8198,19 +8213,19 @@
         <v>314</v>
       </c>
       <c r="B310" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C310" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D310" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="E310" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F310" t="s">
-        <v>1175</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -8218,19 +8233,19 @@
         <v>315</v>
       </c>
       <c r="B311" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C311" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D311" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E311" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F311" t="s">
-        <v>1176</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -8238,10 +8253,10 @@
         <v>316</v>
       </c>
       <c r="E312" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F312" t="s">
-        <v>1177</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -8249,16 +8264,16 @@
         <v>317</v>
       </c>
       <c r="B313" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C313" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E313" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F313" t="s">
-        <v>1178</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -8266,27 +8281,30 @@
         <v>318</v>
       </c>
       <c r="B314" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C314" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E314" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F314" t="s">
-        <v>1179</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>319</v>
       </c>
+      <c r="B315" t="s">
+        <v>577</v>
+      </c>
       <c r="E315" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F315" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -8294,19 +8312,19 @@
         <v>320</v>
       </c>
       <c r="B316" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C316" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D316" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="E316" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F316" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -8314,19 +8332,19 @@
         <v>321</v>
       </c>
       <c r="B317" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C317" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D317" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="E317" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F317" t="s">
-        <v>1182</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -8334,10 +8352,10 @@
         <v>322</v>
       </c>
       <c r="E318" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F318" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8345,19 +8363,19 @@
         <v>323</v>
       </c>
       <c r="B319" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C319" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D319" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E319" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F319" t="s">
-        <v>1184</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -8365,10 +8383,10 @@
         <v>324</v>
       </c>
       <c r="E320" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F320" t="s">
-        <v>1185</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8376,10 +8394,10 @@
         <v>325</v>
       </c>
       <c r="E321" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F321" t="s">
-        <v>1186</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -8387,19 +8405,19 @@
         <v>326</v>
       </c>
       <c r="B322" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C322" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D322" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="E322" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F322" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -8407,10 +8425,10 @@
         <v>327</v>
       </c>
       <c r="E323" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F323" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -8418,19 +8436,19 @@
         <v>328</v>
       </c>
       <c r="B324" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C324" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D324" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="E324" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F324" t="s">
-        <v>1189</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8438,19 +8456,19 @@
         <v>329</v>
       </c>
       <c r="B325" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C325" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D325" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="E325" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F325" t="s">
-        <v>1190</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8458,13 +8476,13 @@
         <v>330</v>
       </c>
       <c r="B326" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E326" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F326" t="s">
-        <v>1191</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -8472,19 +8490,19 @@
         <v>331</v>
       </c>
       <c r="B327" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C327" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D327" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="E327" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F327" t="s">
-        <v>1192</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -8492,19 +8510,19 @@
         <v>332</v>
       </c>
       <c r="B328" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C328" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D328" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E328" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F328" t="s">
-        <v>1193</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8512,16 +8530,16 @@
         <v>333</v>
       </c>
       <c r="B329" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C329" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D329" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="E329" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F329" t="s">
         <v>333</v>
@@ -8532,16 +8550,16 @@
         <v>334</v>
       </c>
       <c r="B330" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C330" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="E330" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F330" t="s">
-        <v>1194</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -8549,19 +8567,19 @@
         <v>335</v>
       </c>
       <c r="B331" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C331" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D331" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="E331" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F331" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -8569,16 +8587,16 @@
         <v>336</v>
       </c>
       <c r="B332" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C332" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D332" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E332" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F332" t="s">
         <v>336</v>
@@ -8589,19 +8607,19 @@
         <v>337</v>
       </c>
       <c r="B333" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C333" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D333" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E333" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F333" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8609,19 +8627,19 @@
         <v>338</v>
       </c>
       <c r="B334" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C334" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D334" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="E334" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F334" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8629,10 +8647,10 @@
         <v>339</v>
       </c>
       <c r="E335" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F335" t="s">
-        <v>1198</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -8640,13 +8658,13 @@
         <v>340</v>
       </c>
       <c r="B336" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E336" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F336" t="s">
-        <v>1199</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -8654,19 +8672,19 @@
         <v>341</v>
       </c>
       <c r="B337" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C337" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D337" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="E337" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F337" t="s">
-        <v>1200</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -8674,13 +8692,13 @@
         <v>342</v>
       </c>
       <c r="B338" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E338" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F338" t="s">
-        <v>1201</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -8688,16 +8706,16 @@
         <v>343</v>
       </c>
       <c r="B339" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C339" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D339" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E339" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F339" t="s">
         <v>343</v>
@@ -8708,10 +8726,10 @@
         <v>344</v>
       </c>
       <c r="E340" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F340" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -8719,10 +8737,10 @@
         <v>345</v>
       </c>
       <c r="E341" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F341" t="s">
-        <v>1203</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -8730,13 +8748,13 @@
         <v>346</v>
       </c>
       <c r="B342" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E342" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F342" t="s">
-        <v>1204</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -8744,19 +8762,19 @@
         <v>347</v>
       </c>
       <c r="B343" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C343" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D343" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="E343" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F343" t="s">
-        <v>1205</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -8764,19 +8782,19 @@
         <v>348</v>
       </c>
       <c r="B344" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C344" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D344" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="E344" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F344" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -8784,19 +8802,19 @@
         <v>349</v>
       </c>
       <c r="B345" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C345" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D345" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="E345" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F345" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -8804,19 +8822,19 @@
         <v>350</v>
       </c>
       <c r="B346" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C346" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D346" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="E346" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F346" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -8824,10 +8842,10 @@
         <v>351</v>
       </c>
       <c r="E347" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F347" t="s">
-        <v>1209</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -8835,19 +8853,19 @@
         <v>352</v>
       </c>
       <c r="B348" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C348" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D348" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="E348" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F348" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -8855,16 +8873,16 @@
         <v>353</v>
       </c>
       <c r="B349" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C349" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D349" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E349" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F349" t="s">
         <v>353</v>
@@ -8875,16 +8893,16 @@
         <v>354</v>
       </c>
       <c r="B350" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C350" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D350" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E350" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F350" t="s">
         <v>354</v>
@@ -8895,16 +8913,16 @@
         <v>355</v>
       </c>
       <c r="B351" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C351" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D351" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E351" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F351" t="s">
         <v>355</v>
@@ -8915,16 +8933,16 @@
         <v>356</v>
       </c>
       <c r="B352" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C352" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D352" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="E352" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F352" t="s">
         <v>356</v>
@@ -8935,19 +8953,19 @@
         <v>357</v>
       </c>
       <c r="B353" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C353" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D353" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="E353" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F353" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -8955,19 +8973,19 @@
         <v>358</v>
       </c>
       <c r="B354" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C354" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D354" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="E354" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F354" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -8975,19 +8993,19 @@
         <v>359</v>
       </c>
       <c r="B355" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C355" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D355" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="E355" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F355" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -8995,19 +9013,19 @@
         <v>360</v>
       </c>
       <c r="B356" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C356" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D356" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="E356" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F356" t="s">
-        <v>1214</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -9015,10 +9033,10 @@
         <v>361</v>
       </c>
       <c r="E357" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F357" t="s">
-        <v>1215</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -9026,19 +9044,19 @@
         <v>362</v>
       </c>
       <c r="B358" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C358" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D358" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="E358" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F358" t="s">
-        <v>1216</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -9046,16 +9064,16 @@
         <v>363</v>
       </c>
       <c r="B359" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C359" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E359" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F359" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -9063,16 +9081,16 @@
         <v>364</v>
       </c>
       <c r="B360" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C360" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E360" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F360" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -9080,16 +9098,16 @@
         <v>365</v>
       </c>
       <c r="B361" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C361" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D361" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="E361" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F361" t="s">
         <v>365</v>
@@ -9100,19 +9118,19 @@
         <v>366</v>
       </c>
       <c r="B362" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C362" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D362" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="E362" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F362" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -9120,13 +9138,13 @@
         <v>367</v>
       </c>
       <c r="C363" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E363" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F363" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -9134,13 +9152,13 @@
         <v>368</v>
       </c>
       <c r="C364" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E364" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F364" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="365" spans="1:6">
@@ -9148,13 +9166,13 @@
         <v>369</v>
       </c>
       <c r="C365" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E365" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F365" t="s">
-        <v>1222</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -9162,16 +9180,16 @@
         <v>370</v>
       </c>
       <c r="B366" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C366" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D366" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E366" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F366" t="s">
         <v>370</v>
@@ -9182,16 +9200,16 @@
         <v>371</v>
       </c>
       <c r="B367" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C367" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D367" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E367" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F367" t="s">
         <v>371</v>
@@ -9202,19 +9220,19 @@
         <v>372</v>
       </c>
       <c r="B368" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C368" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D368" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="E368" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F368" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -9222,13 +9240,13 @@
         <v>373</v>
       </c>
       <c r="B369" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E369" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F369" t="s">
-        <v>1224</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -9236,13 +9254,13 @@
         <v>374</v>
       </c>
       <c r="C370" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E370" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F370" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -9250,16 +9268,16 @@
         <v>375</v>
       </c>
       <c r="B371" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C371" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D371" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E371" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F371" t="s">
         <v>375</v>
@@ -9270,16 +9288,16 @@
         <v>376</v>
       </c>
       <c r="B372" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C372" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D372" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="E372" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F372" t="s">
         <v>376</v>
@@ -9290,16 +9308,16 @@
         <v>377</v>
       </c>
       <c r="B373" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C373" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D373" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="E373" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F373" t="s">
         <v>377</v>
@@ -9310,16 +9328,16 @@
         <v>378</v>
       </c>
       <c r="B374" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C374" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D374" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="E374" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F374" t="s">
         <v>378</v>
@@ -9330,16 +9348,16 @@
         <v>379</v>
       </c>
       <c r="B375" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C375" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D375" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="E375" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F375" t="s">
         <v>379</v>
@@ -9350,16 +9368,16 @@
         <v>380</v>
       </c>
       <c r="B376" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C376" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D376" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="E376" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F376" t="s">
         <v>380</v>
@@ -9370,19 +9388,19 @@
         <v>381</v>
       </c>
       <c r="B377" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C377" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D377" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="E377" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F377" t="s">
-        <v>1226</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -9390,19 +9408,19 @@
         <v>382</v>
       </c>
       <c r="B378" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C378" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D378" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E378" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F378" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -9410,16 +9428,16 @@
         <v>383</v>
       </c>
       <c r="B379" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C379" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D379" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="E379" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F379" t="s">
         <v>383</v>
@@ -9430,19 +9448,19 @@
         <v>384</v>
       </c>
       <c r="B380" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C380" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D380" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="E380" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F380" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -9450,16 +9468,16 @@
         <v>385</v>
       </c>
       <c r="B381" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C381" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D381" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="E381" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F381" t="s">
         <v>385</v>
@@ -9470,19 +9488,19 @@
         <v>386</v>
       </c>
       <c r="B382" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C382" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D382" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="E382" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F382" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -9490,19 +9508,19 @@
         <v>387</v>
       </c>
       <c r="B383" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C383" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D383" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="E383" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F383" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -9510,19 +9528,19 @@
         <v>388</v>
       </c>
       <c r="B384" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C384" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D384" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E384" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F384" t="s">
-        <v>1231</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -9530,10 +9548,10 @@
         <v>389</v>
       </c>
       <c r="E385" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F385" t="s">
-        <v>1232</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -9541,10 +9559,10 @@
         <v>390</v>
       </c>
       <c r="E386" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F386" t="s">
-        <v>1233</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -9552,16 +9570,16 @@
         <v>391</v>
       </c>
       <c r="B387" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C387" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E387" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F387" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -9569,19 +9587,19 @@
         <v>392</v>
       </c>
       <c r="B388" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C388" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D388" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E388" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F388" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -9589,19 +9607,19 @@
         <v>393</v>
       </c>
       <c r="B389" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C389" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D389" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="E389" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F389" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -9609,19 +9627,19 @@
         <v>394</v>
       </c>
       <c r="B390" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C390" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D390" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="E390" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F390" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -9629,19 +9647,19 @@
         <v>395</v>
       </c>
       <c r="B391" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C391" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D391" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E391" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F391" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -9649,19 +9667,19 @@
         <v>396</v>
       </c>
       <c r="B392" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C392" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D392" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E392" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F392" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -9669,19 +9687,19 @@
         <v>397</v>
       </c>
       <c r="B393" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C393" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D393" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E393" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F393" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -9689,19 +9707,19 @@
         <v>398</v>
       </c>
       <c r="B394" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C394" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D394" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E394" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F394" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="395" spans="1:6">
@@ -9709,16 +9727,16 @@
         <v>399</v>
       </c>
       <c r="B395" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C395" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D395" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E395" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F395" t="s">
         <v>399</v>
@@ -9729,16 +9747,16 @@
         <v>400</v>
       </c>
       <c r="B396" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C396" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D396" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E396" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F396" t="s">
         <v>400</v>
@@ -9749,16 +9767,16 @@
         <v>401</v>
       </c>
       <c r="B397" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C397" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D397" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="E397" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F397" t="s">
         <v>401</v>
@@ -9769,19 +9787,19 @@
         <v>402</v>
       </c>
       <c r="B398" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C398" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D398" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="E398" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F398" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="399" spans="1:6">
@@ -9789,19 +9807,19 @@
         <v>403</v>
       </c>
       <c r="B399" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C399" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D399" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E399" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F399" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -9809,19 +9827,19 @@
         <v>404</v>
       </c>
       <c r="B400" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C400" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D400" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="E400" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F400" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -9829,19 +9847,19 @@
         <v>405</v>
       </c>
       <c r="B401" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C401" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D401" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="E401" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F401" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -9849,19 +9867,19 @@
         <v>406</v>
       </c>
       <c r="B402" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C402" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D402" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="E402" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F402" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="403" spans="1:6">
@@ -9869,16 +9887,16 @@
         <v>407</v>
       </c>
       <c r="B403" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C403" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="E403" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F403" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -9886,19 +9904,19 @@
         <v>408</v>
       </c>
       <c r="B404" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C404" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D404" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="E404" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F404" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -9906,19 +9924,19 @@
         <v>409</v>
       </c>
       <c r="B405" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C405" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D405" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="E405" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F405" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -9926,16 +9944,16 @@
         <v>410</v>
       </c>
       <c r="B406" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C406" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E406" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F406" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -9943,16 +9961,16 @@
         <v>411</v>
       </c>
       <c r="B407" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C407" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E407" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F407" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9960,16 +9978,16 @@
         <v>412</v>
       </c>
       <c r="B408" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C408" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E408" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F408" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -9977,19 +9995,19 @@
         <v>413</v>
       </c>
       <c r="B409" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C409" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D409" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="E409" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F409" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -9997,19 +10015,19 @@
         <v>414</v>
       </c>
       <c r="B410" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C410" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="D410" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="E410" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F410" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -10017,19 +10035,19 @@
         <v>415</v>
       </c>
       <c r="B411" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C411" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D411" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="E411" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F411" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -10037,19 +10055,19 @@
         <v>416</v>
       </c>
       <c r="B412" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C412" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D412" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="E412" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F412" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -10057,19 +10075,19 @@
         <v>417</v>
       </c>
       <c r="B413" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C413" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D413" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E413" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F413" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -10077,16 +10095,16 @@
         <v>418</v>
       </c>
       <c r="B414" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C414" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E414" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F414" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -10094,16 +10112,16 @@
         <v>419</v>
       </c>
       <c r="B415" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C415" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D415" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="E415" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F415" t="s">
         <v>419</v>
@@ -10114,16 +10132,16 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C416" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E416" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F416" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -10131,16 +10149,16 @@
         <v>421</v>
       </c>
       <c r="B417" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C417" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E417" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F417" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -10148,16 +10166,16 @@
         <v>422</v>
       </c>
       <c r="B418" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C418" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E418" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F418" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -10165,16 +10183,16 @@
         <v>423</v>
       </c>
       <c r="B419" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C419" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E419" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F419" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -10182,16 +10200,16 @@
         <v>424</v>
       </c>
       <c r="B420" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C420" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E420" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F420" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -10199,10 +10217,10 @@
         <v>425</v>
       </c>
       <c r="E421" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F421" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -10210,10 +10228,10 @@
         <v>426</v>
       </c>
       <c r="E422" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F422" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -10221,10 +10239,10 @@
         <v>427</v>
       </c>
       <c r="E423" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F423" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -10232,10 +10250,10 @@
         <v>428</v>
       </c>
       <c r="E424" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F424" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -10243,10 +10261,10 @@
         <v>429</v>
       </c>
       <c r="E425" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F425" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -10254,10 +10272,10 @@
         <v>430</v>
       </c>
       <c r="E426" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F426" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -10265,19 +10283,19 @@
         <v>431</v>
       </c>
       <c r="B427" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C427" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D427" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="E427" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F427" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -10285,10 +10303,10 @@
         <v>432</v>
       </c>
       <c r="E428" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F428" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -10296,10 +10314,10 @@
         <v>433</v>
       </c>
       <c r="E429" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F429" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -10307,10 +10325,10 @@
         <v>434</v>
       </c>
       <c r="E430" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F430" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -10318,10 +10336,10 @@
         <v>435</v>
       </c>
       <c r="E431" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F431" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -10329,10 +10347,10 @@
         <v>436</v>
       </c>
       <c r="E432" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F432" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -10340,19 +10358,19 @@
         <v>437</v>
       </c>
       <c r="B433" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C433" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D433" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="E433" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F433" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -10360,16 +10378,16 @@
         <v>438</v>
       </c>
       <c r="B434" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C434" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D434" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="E434" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F434" t="s">
         <v>438</v>
@@ -10380,19 +10398,19 @@
         <v>439</v>
       </c>
       <c r="B435" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C435" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D435" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="E435" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F435" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -10400,16 +10418,16 @@
         <v>440</v>
       </c>
       <c r="B436" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C436" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E436" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F436" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -10417,16 +10435,16 @@
         <v>441</v>
       </c>
       <c r="B437" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C437" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E437" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F437" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -10434,16 +10452,16 @@
         <v>442</v>
       </c>
       <c r="B438" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C438" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E438" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F438" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -10451,16 +10469,16 @@
         <v>443</v>
       </c>
       <c r="B439" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C439" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E439" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F439" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -10468,13 +10486,13 @@
         <v>444</v>
       </c>
       <c r="B440" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E440" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F440" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -10482,19 +10500,19 @@
         <v>445</v>
       </c>
       <c r="B441" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C441" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D441" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="E441" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F441" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="442" spans="1:6">
@@ -10502,16 +10520,16 @@
         <v>446</v>
       </c>
       <c r="B442" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C442" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E442" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F442" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -10519,19 +10537,19 @@
         <v>447</v>
       </c>
       <c r="B443" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C443" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D443" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="E443" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F443" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="444" spans="1:6">
@@ -10539,10 +10557,10 @@
         <v>448</v>
       </c>
       <c r="E444" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F444" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -10550,10 +10568,10 @@
         <v>449</v>
       </c>
       <c r="E445" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F445" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="446" spans="1:6">
@@ -10561,16 +10579,16 @@
         <v>450</v>
       </c>
       <c r="B446" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C446" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D446" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E446" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F446" t="s">
         <v>450</v>
@@ -10581,16 +10599,16 @@
         <v>451</v>
       </c>
       <c r="B447" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C447" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D447" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="E447" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F447" t="s">
         <v>451</v>
@@ -10601,16 +10619,16 @@
         <v>452</v>
       </c>
       <c r="B448" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C448" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D448" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="E448" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F448" t="s">
         <v>452</v>
@@ -10621,16 +10639,16 @@
         <v>453</v>
       </c>
       <c r="B449" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C449" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D449" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="E449" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F449" t="s">
         <v>453</v>
@@ -10641,19 +10659,19 @@
         <v>454</v>
       </c>
       <c r="B450" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C450" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D450" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="E450" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F450" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="451" spans="1:6">
@@ -10661,16 +10679,16 @@
         <v>455</v>
       </c>
       <c r="B451" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C451" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D451" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="E451" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F451" t="s">
         <v>455</v>
@@ -10681,19 +10699,19 @@
         <v>456</v>
       </c>
       <c r="B452" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C452" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D452" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="E452" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F452" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -10701,10 +10719,10 @@
         <v>457</v>
       </c>
       <c r="E453" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F453" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="454" spans="1:6">
@@ -10712,19 +10730,19 @@
         <v>458</v>
       </c>
       <c r="B454" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C454" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D454" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="E454" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F454" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -10732,19 +10750,19 @@
         <v>459</v>
       </c>
       <c r="B455" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C455" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D455" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="E455" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F455" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="456" spans="1:6">
@@ -10752,16 +10770,16 @@
         <v>460</v>
       </c>
       <c r="B456" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C456" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E456" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F456" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -10769,16 +10787,16 @@
         <v>461</v>
       </c>
       <c r="B457" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C457" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E457" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F457" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="458" spans="1:6">
@@ -10786,16 +10804,16 @@
         <v>462</v>
       </c>
       <c r="B458" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C458" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E458" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F458" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -10803,16 +10821,16 @@
         <v>463</v>
       </c>
       <c r="B459" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C459" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E459" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F459" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="460" spans="1:6">
@@ -10820,16 +10838,16 @@
         <v>464</v>
       </c>
       <c r="B460" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C460" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E460" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F460" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -10837,16 +10855,16 @@
         <v>465</v>
       </c>
       <c r="B461" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C461" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E461" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F461" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="462" spans="1:6">
@@ -10854,16 +10872,16 @@
         <v>466</v>
       </c>
       <c r="B462" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C462" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E462" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F462" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="463" spans="1:6">
@@ -10871,16 +10889,16 @@
         <v>467</v>
       </c>
       <c r="B463" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C463" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E463" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F463" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="464" spans="1:6">
@@ -10888,16 +10906,16 @@
         <v>468</v>
       </c>
       <c r="B464" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C464" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E464" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F464" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -10905,16 +10923,16 @@
         <v>469</v>
       </c>
       <c r="B465" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C465" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E465" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F465" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -10922,10 +10940,10 @@
         <v>470</v>
       </c>
       <c r="E466" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F466" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -10933,10 +10951,10 @@
         <v>471</v>
       </c>
       <c r="E467" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F467" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="468" spans="1:6">
@@ -10944,10 +10962,10 @@
         <v>472</v>
       </c>
       <c r="E468" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F468" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -10955,10 +10973,10 @@
         <v>473</v>
       </c>
       <c r="E469" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F469" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -10966,10 +10984,10 @@
         <v>474</v>
       </c>
       <c r="E470" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F470" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -10977,19 +10995,19 @@
         <v>475</v>
       </c>
       <c r="B471" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C471" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D471" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="E471" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F471" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -10997,16 +11015,16 @@
         <v>476</v>
       </c>
       <c r="B472" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C472" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D472" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="E472" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F472" t="s">
         <v>476</v>
@@ -11017,16 +11035,16 @@
         <v>477</v>
       </c>
       <c r="B473" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C473" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D473" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="E473" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F473" t="s">
         <v>477</v>
@@ -11037,16 +11055,16 @@
         <v>478</v>
       </c>
       <c r="B474" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C474" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D474" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="E474" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F474" t="s">
         <v>478</v>
@@ -11057,19 +11075,19 @@
         <v>479</v>
       </c>
       <c r="B475" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C475" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D475" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="E475" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F475" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="476" spans="1:6">
@@ -11077,19 +11095,19 @@
         <v>480</v>
       </c>
       <c r="B476" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C476" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D476" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="E476" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F476" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -11097,16 +11115,16 @@
         <v>481</v>
       </c>
       <c r="B477" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C477" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D477" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="E477" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F477" t="s">
         <v>481</v>
@@ -11117,16 +11135,16 @@
         <v>482</v>
       </c>
       <c r="B478" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C478" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D478" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="E478" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F478" t="s">
         <v>482</v>
@@ -11137,19 +11155,19 @@
         <v>483</v>
       </c>
       <c r="B479" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C479" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D479" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="E479" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F479" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -11157,16 +11175,16 @@
         <v>484</v>
       </c>
       <c r="B480" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C480" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D480" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="E480" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F480" t="s">
         <v>484</v>
@@ -11177,10 +11195,10 @@
         <v>485</v>
       </c>
       <c r="E481" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F481" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="482" spans="1:6">
@@ -11188,10 +11206,10 @@
         <v>486</v>
       </c>
       <c r="E482" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F482" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -11199,19 +11217,19 @@
         <v>487</v>
       </c>
       <c r="B483" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C483" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="D483" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="E483" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F483" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="484" spans="1:6">
@@ -11219,19 +11237,19 @@
         <v>488</v>
       </c>
       <c r="B484" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C484" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D484" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="E484" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F484" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -11239,16 +11257,16 @@
         <v>489</v>
       </c>
       <c r="B485" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C485" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D485" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="E485" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F485" t="s">
         <v>489</v>
@@ -11259,10 +11277,10 @@
         <v>490</v>
       </c>
       <c r="E486" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F486" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="487" spans="1:6">
@@ -11270,7 +11288,7 @@
         <v>491</v>
       </c>
       <c r="F487" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="488" spans="1:6">
@@ -11278,7 +11296,7 @@
         <v>492</v>
       </c>
       <c r="F488" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -11286,7 +11304,7 @@
         <v>493</v>
       </c>
       <c r="F489" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="490" spans="1:6">
@@ -11294,19 +11312,19 @@
         <v>494</v>
       </c>
       <c r="B490" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C490" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D490" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="E490" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F490" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="491" spans="1:6">
@@ -11314,19 +11332,19 @@
         <v>495</v>
       </c>
       <c r="B491" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C491" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D491" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="E491" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F491" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="492" spans="1:6">
@@ -11334,19 +11352,19 @@
         <v>496</v>
       </c>
       <c r="B492" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C492" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D492" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E492" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F492" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -11354,19 +11372,19 @@
         <v>497</v>
       </c>
       <c r="B493" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C493" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D493" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="E493" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F493" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="494" spans="1:6">
@@ -11374,19 +11392,19 @@
         <v>498</v>
       </c>
       <c r="B494" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C494" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D494" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="E494" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F494" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -11394,19 +11412,19 @@
         <v>499</v>
       </c>
       <c r="B495" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C495" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D495" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="E495" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F495" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="496" spans="1:6">
@@ -11414,19 +11432,19 @@
         <v>500</v>
       </c>
       <c r="B496" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C496" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D496" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="E496" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F496" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="497" spans="1:6">
@@ -11437,13 +11455,13 @@
         <v>501</v>
       </c>
       <c r="C497" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E497" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F497" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="498" spans="1:6">
@@ -11451,19 +11469,19 @@
         <v>502</v>
       </c>
       <c r="B498" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C498" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D498" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E498" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F498" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -11471,19 +11489,19 @@
         <v>503</v>
       </c>
       <c r="B499" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C499" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D499" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="E499" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F499" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="500" spans="1:6">
@@ -11491,19 +11509,19 @@
         <v>504</v>
       </c>
       <c r="B500" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C500" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D500" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E500" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F500" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -11511,19 +11529,19 @@
         <v>505</v>
       </c>
       <c r="B501" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C501" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D501" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E501" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F501" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="502" spans="1:6">
@@ -11531,19 +11549,19 @@
         <v>506</v>
       </c>
       <c r="B502" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C502" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D502" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E502" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F502" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -11551,19 +11569,19 @@
         <v>507</v>
       </c>
       <c r="B503" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C503" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D503" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="E503" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F503" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="504" spans="1:6">
@@ -11574,7 +11592,7 @@
         <v>508</v>
       </c>
       <c r="E504" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F504" t="s">
         <v>508</v>
@@ -11588,7 +11606,7 @@
         <v>509</v>
       </c>
       <c r="E505" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F505" t="s">
         <v>509</v>
@@ -11599,19 +11617,13 @@
         <v>510</v>
       </c>
       <c r="B506" t="s">
-        <v>721</v>
-      </c>
-      <c r="C506" t="s">
-        <v>748</v>
-      </c>
-      <c r="D506" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="E506" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F506" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="507" spans="1:6">
@@ -11619,19 +11631,13 @@
         <v>511</v>
       </c>
       <c r="B507" t="s">
-        <v>722</v>
-      </c>
-      <c r="C507" t="s">
-        <v>748</v>
-      </c>
-      <c r="D507" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
       <c r="E507" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F507" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="508" spans="1:6">
@@ -11639,19 +11645,13 @@
         <v>512</v>
       </c>
       <c r="B508" t="s">
-        <v>723</v>
-      </c>
-      <c r="C508" t="s">
-        <v>748</v>
-      </c>
-      <c r="D508" t="s">
-        <v>748</v>
+        <v>726</v>
       </c>
       <c r="E508" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F508" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -11659,19 +11659,13 @@
         <v>513</v>
       </c>
       <c r="B509" t="s">
-        <v>724</v>
-      </c>
-      <c r="C509" t="s">
-        <v>748</v>
-      </c>
-      <c r="D509" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="E509" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F509" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -11679,19 +11673,13 @@
         <v>514</v>
       </c>
       <c r="B510" t="s">
-        <v>725</v>
-      </c>
-      <c r="C510" t="s">
-        <v>748</v>
-      </c>
-      <c r="D510" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="E510" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F510" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -11699,19 +11687,13 @@
         <v>515</v>
       </c>
       <c r="B511" t="s">
-        <v>726</v>
-      </c>
-      <c r="C511" t="s">
-        <v>748</v>
-      </c>
-      <c r="D511" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="E511" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F511" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="512" spans="1:6">
@@ -11719,19 +11701,13 @@
         <v>516</v>
       </c>
       <c r="B512" t="s">
-        <v>727</v>
-      </c>
-      <c r="C512" t="s">
-        <v>748</v>
-      </c>
-      <c r="D512" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="E512" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F512" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -11739,19 +11715,13 @@
         <v>517</v>
       </c>
       <c r="B513" t="s">
-        <v>728</v>
-      </c>
-      <c r="C513" t="s">
-        <v>748</v>
-      </c>
-      <c r="D513" t="s">
-        <v>748</v>
+        <v>731</v>
       </c>
       <c r="E513" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F513" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -11759,19 +11729,19 @@
         <v>518</v>
       </c>
       <c r="B514" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C514" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D514" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E514" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F514" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="515" spans="1:6">
@@ -11779,19 +11749,19 @@
         <v>519</v>
       </c>
       <c r="B515" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C515" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D515" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E515" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F515" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="516" spans="1:6">
@@ -11799,19 +11769,19 @@
         <v>520</v>
       </c>
       <c r="B516" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C516" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D516" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E516" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F516" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="517" spans="1:6">
@@ -11819,19 +11789,19 @@
         <v>521</v>
       </c>
       <c r="B517" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C517" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D517" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E517" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F517" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -11839,19 +11809,19 @@
         <v>522</v>
       </c>
       <c r="B518" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C518" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="D518" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="E518" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F518" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="519" spans="1:6">
@@ -11859,19 +11829,13 @@
         <v>523</v>
       </c>
       <c r="B519" t="s">
-        <v>734</v>
-      </c>
-      <c r="C519" t="s">
-        <v>748</v>
-      </c>
-      <c r="D519" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="E519" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F519" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="520" spans="1:6">
@@ -11879,19 +11843,13 @@
         <v>524</v>
       </c>
       <c r="B520" t="s">
-        <v>735</v>
-      </c>
-      <c r="C520" t="s">
-        <v>748</v>
-      </c>
-      <c r="D520" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="E520" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F520" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="521" spans="1:6">
@@ -11899,19 +11857,13 @@
         <v>525</v>
       </c>
       <c r="B521" t="s">
-        <v>736</v>
-      </c>
-      <c r="C521" t="s">
-        <v>748</v>
-      </c>
-      <c r="D521" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="E521" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F521" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="522" spans="1:6">
@@ -11919,19 +11871,13 @@
         <v>526</v>
       </c>
       <c r="B522" t="s">
-        <v>737</v>
-      </c>
-      <c r="C522" t="s">
-        <v>748</v>
-      </c>
-      <c r="D522" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="E522" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F522" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="523" spans="1:6">
@@ -11939,19 +11885,13 @@
         <v>527</v>
       </c>
       <c r="B523" t="s">
-        <v>738</v>
-      </c>
-      <c r="C523" t="s">
-        <v>748</v>
-      </c>
-      <c r="D523" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="E523" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F523" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="524" spans="1:6">
@@ -11959,19 +11899,53 @@
         <v>528</v>
       </c>
       <c r="B524" t="s">
-        <v>739</v>
-      </c>
-      <c r="C524" t="s">
-        <v>748</v>
-      </c>
-      <c r="D524" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="E524" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="F524" t="s">
-        <v>1034</v>
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
+      <c r="A525" t="s">
+        <v>529</v>
+      </c>
+      <c r="B525" t="s">
+        <v>743</v>
+      </c>
+      <c r="C525" t="s">
+        <v>753</v>
+      </c>
+      <c r="D525" t="s">
+        <v>753</v>
+      </c>
+      <c r="E525" t="s">
+        <v>887</v>
+      </c>
+      <c r="F525" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
+      <c r="A526" t="s">
+        <v>530</v>
+      </c>
+      <c r="B526" t="s">
+        <v>744</v>
+      </c>
+      <c r="C526" t="s">
+        <v>753</v>
+      </c>
+      <c r="D526" t="s">
+        <v>753</v>
+      </c>
+      <c r="E526" t="s">
+        <v>887</v>
+      </c>
+      <c r="F526" t="s">
+        <v>1185</v>
       </c>
     </row>
   </sheetData>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F527"/>
+  <dimension ref="A1:F528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13340,6 +13340,30 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>12-D-6091-07</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>12-D-6091-07</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr"/>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>12-D-6091-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Articulos.xlsx
+++ b/BD_Articulos.xlsx
@@ -1,13 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F528"/>
+  <dimension ref="A1:F534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,9 +645,6 @@
           <t>11-A-6013-01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -666,9 +662,6 @@
           <t>11-A-6013-03</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -792,7 +785,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -820,7 +812,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -838,9 +829,6 @@
           <t>11-A-6102-01</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -858,9 +846,6 @@
           <t>11-A-9012-01</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -878,9 +863,6 @@
           <t>11-A-9023-01</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -898,9 +880,6 @@
           <t>11-A-9024-01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -918,9 +897,6 @@
           <t>11-A-9025-01</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -938,9 +914,6 @@
           <t>11-A-9026-01</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -958,9 +931,6 @@
           <t>11-A-9027-01</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -978,9 +948,6 @@
           <t>11-A-9028-01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -998,9 +965,6 @@
           <t>11-A-9029-01</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1018,9 +982,6 @@
           <t>11-A-9029-02</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1038,9 +999,6 @@
           <t>11-A-9030-01</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1058,9 +1016,6 @@
           <t>11-A-9030-02</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1078,9 +1033,6 @@
           <t>11-A-9040-01</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1098,9 +1050,6 @@
           <t>11-A-9577-01</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1118,9 +1067,16 @@
           <t>11-A-9581-01</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RUN-BACK LUG BRACKET</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Decapado CAL 16 (16 GA)</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1138,9 +1094,6 @@
           <t>11-A-9582-01</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1158,9 +1111,6 @@
           <t>11-A-9794-01</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1178,9 +1128,6 @@
           <t>11-A-9795-01</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1198,9 +1145,6 @@
           <t>11-A-9804-01</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1218,9 +1162,6 @@
           <t>11-A-9807-01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1238,9 +1179,6 @@
           <t>11-A-9813-01</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1258,9 +1196,6 @@
           <t>11-A-9813-02</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1278,9 +1213,6 @@
           <t>11-A-9815-01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1298,9 +1230,6 @@
           <t>11-A-9816-01</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1318,9 +1247,6 @@
           <t>11-A-9830-01</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1338,9 +1264,6 @@
           <t>11-A-9836-01</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1358,9 +1281,6 @@
           <t>11-A-9837-01</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1378,9 +1298,6 @@
           <t>11-A-9843-01</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1398,9 +1315,6 @@
           <t>11-A-9845-01</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1418,9 +1332,6 @@
           <t>11-A-9846-01</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1438,9 +1349,6 @@
           <t>11-A-9847-01</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1458,9 +1366,6 @@
           <t>11-A-9853-01</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1478,9 +1383,6 @@
           <t>11-A-9875-01</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1498,9 +1400,6 @@
           <t>11-A-9875-03</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1518,9 +1417,6 @@
           <t>11-A-9875-07</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1538,9 +1434,6 @@
           <t>11-A-9895-01</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1558,9 +1451,6 @@
           <t>11-A-9897-01</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1578,9 +1468,6 @@
           <t>11-A-9908-01</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1598,9 +1485,6 @@
           <t>11-A-9909-01</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1618,9 +1502,6 @@
           <t>11-A-9916-01</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1638,9 +1519,6 @@
           <t>11-A-9917-01</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1658,13 +1536,11 @@
           <t>11-A-9921-01</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1682,13 +1558,11 @@
           <t>11-A-9923-01</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1706,9 +1580,6 @@
           <t>11-A-9925-01</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1726,9 +1597,6 @@
           <t>11-A-9926-01</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1746,9 +1614,6 @@
           <t>11-A-9927-01</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1766,9 +1631,6 @@
           <t>11-A-9951-01</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1786,9 +1648,6 @@
           <t>11-A-9958-01</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1806,9 +1665,6 @@
           <t>11-A-9959-01</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1826,9 +1682,6 @@
           <t>11-A-9960-01</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1846,9 +1699,6 @@
           <t>11-A-9961-01</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1866,9 +1716,6 @@
           <t>11-A-9983-01</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1918,9 +1765,6 @@
           <t>11-B-9034-01</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1938,9 +1782,6 @@
           <t>11-B-9074-01</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1958,9 +1799,6 @@
           <t>11-B-9079-01</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1978,9 +1816,6 @@
           <t>11-B-9083-01</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -1998,9 +1833,6 @@
           <t>11-B-9085-01</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2018,9 +1850,6 @@
           <t>11-B-9086-01</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2038,9 +1867,6 @@
           <t>11-B-9088-01</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2058,9 +1884,6 @@
           <t>11-B-9123-01</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2078,13 +1901,11 @@
           <t>11-B-9126-01</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2102,13 +1923,11 @@
           <t>11-B-9127-01</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2126,9 +1945,6 @@
           <t>11-B-9147-01</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2146,9 +1962,6 @@
           <t>11-B-9193-01</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2166,9 +1979,6 @@
           <t>11-B-9194-03</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2186,9 +1996,6 @@
           <t>11-B-9194-04</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2206,9 +2013,6 @@
           <t>11-B-9195-01</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2226,9 +2030,6 @@
           <t>11-B-9208-01</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2246,9 +2047,6 @@
           <t>11-B-9208-02</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2266,9 +2064,6 @@
           <t>11-B-9211-01</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2286,9 +2081,6 @@
           <t>11-B-9310-01</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2306,9 +2098,6 @@
           <t>11-B-9311-02</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2326,9 +2115,6 @@
           <t>11-B-9362-01</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2346,9 +2132,6 @@
           <t>11-B-9374-01</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2366,9 +2149,6 @@
           <t>11-B-9411-01</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2386,9 +2166,6 @@
           <t>11-B-9520-01</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2406,9 +2183,6 @@
           <t>11-B-9521-01</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2426,9 +2200,6 @@
           <t>11-B-9528-01</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2446,9 +2217,6 @@
           <t>11-B-9618-01</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2466,9 +2234,6 @@
           <t>11-B-9620-01</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2486,9 +2251,6 @@
           <t>11-B-9697-01</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2506,9 +2268,6 @@
           <t>11-B-9743-01</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2526,9 +2285,6 @@
           <t>11-B-9743-02</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2546,9 +2302,6 @@
           <t>11-B-9753-01</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2566,9 +2319,6 @@
           <t>11-B-9754-01</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2586,9 +2336,6 @@
           <t>11-B-9754-02</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2606,9 +2353,6 @@
           <t>11-B-9755-01</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2658,9 +2402,6 @@
           <t>11-C-9115-01</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2678,9 +2419,6 @@
           <t>11-C-9115-02</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2698,9 +2436,6 @@
           <t>11-C-9229-01</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2718,9 +2453,6 @@
           <t>11-C-9230-01</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2738,9 +2470,6 @@
           <t>11-C-9231-01</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2758,9 +2487,6 @@
           <t>11-C-9232-01</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2778,9 +2504,6 @@
           <t>11-C-9233-01</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2798,9 +2521,6 @@
           <t>11-C-9233-02</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2818,13 +2538,11 @@
           <t>11-C-9241-01</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2842,13 +2560,11 @@
           <t>11-C-9241-02</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2866,13 +2582,11 @@
           <t>11-C-9242-01</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2890,13 +2604,11 @@
           <t>11-C-9242-02</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2914,9 +2626,6 @@
           <t>11-C-9243-01</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2934,13 +2643,11 @@
           <t>11-C-9244-01</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2958,9 +2665,6 @@
           <t>11-C-9245-01</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2978,9 +2682,6 @@
           <t>11-C-9246-01</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -2998,13 +2699,11 @@
           <t>11-C-9247-01</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3022,13 +2721,11 @@
           <t>11-C-9248-01</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3046,9 +2743,6 @@
           <t>11-C-9249-01</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3066,9 +2760,6 @@
           <t>11-C-9250-01</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3086,9 +2777,6 @@
           <t>11-C-9277-02</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3106,9 +2794,6 @@
           <t>11-C-9280-01</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3126,9 +2811,6 @@
           <t>11-C-9281-01</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3146,9 +2828,6 @@
           <t>11-C-9282-01</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3166,9 +2845,6 @@
           <t>11-C-9283-01</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3186,9 +2862,6 @@
           <t>11-C-9284-01</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3206,9 +2879,6 @@
           <t>11-C-9285-01</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3226,13 +2896,11 @@
           <t>11-C-9300-01</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3250,13 +2918,11 @@
           <t>11-C-9307-01</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3274,13 +2940,11 @@
           <t>11-C-9333-01</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3298,13 +2962,11 @@
           <t>11-C-9352-01</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3322,9 +2984,6 @@
           <t>11-C-9576-02</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3342,9 +3001,6 @@
           <t>11-C-9582-01</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3362,13 +3018,11 @@
           <t>11-C-9611-01</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3386,13 +3040,11 @@
           <t>11-C-9612-01</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3410,13 +3062,11 @@
           <t>11-C-9617-01</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3434,13 +3084,11 @@
           <t>11-C-9618-01</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3458,9 +3106,6 @@
           <t>11-C-9620-01</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3478,9 +3123,6 @@
           <t>11-C-9621-01</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3498,13 +3140,11 @@
           <t>11-C-9634-01</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3522,13 +3162,11 @@
           <t>11-C-9638-01</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3546,13 +3184,11 @@
           <t>11-C-9639-01</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3570,13 +3206,11 @@
           <t>11-C-9639-02</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3594,9 +3228,6 @@
           <t>11-C-9665-01</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3614,9 +3245,6 @@
           <t>11-C-9666-01</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3634,13 +3262,11 @@
           <t>11-C-9669-01</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3658,13 +3284,11 @@
           <t>11-C-9681-01</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3682,13 +3306,11 @@
           <t>11-C-9681-02</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3706,9 +3328,6 @@
           <t>11-C-9708-01</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3726,9 +3345,6 @@
           <t>11-C-9709-01</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3746,9 +3362,6 @@
           <t>11-C-9746-01</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3766,9 +3379,6 @@
           <t>11-C-9747-01</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3786,9 +3396,6 @@
           <t>11-C-9778-01</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3806,9 +3413,6 @@
           <t>11-C-9779-01</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3826,9 +3430,6 @@
           <t>11-C-9831-01</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3846,9 +3447,6 @@
           <t>11-C-9832-01</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3866,9 +3464,6 @@
           <t>11-C-9924-01</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3886,13 +3481,11 @@
           <t>11-C-9926-01</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3910,13 +3503,11 @@
           <t>11-C-9943-02</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3934,13 +3525,11 @@
           <t>11-C-9944-01</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3958,9 +3547,6 @@
           <t>11-C-9962-01</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -3978,9 +3564,6 @@
           <t>11-C-9977-01</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4003,8 +3586,6 @@
           <t>11-D-3385-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4128,7 +3709,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -4210,9 +3790,6 @@
           <t>11-D-6245-02</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4230,9 +3807,6 @@
           <t>11-D-6246-03</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4250,9 +3824,6 @@
           <t>11-D-6246-04</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4270,9 +3841,6 @@
           <t>11-D-6252-03</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4290,9 +3858,6 @@
           <t>11-D-6252-05</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4310,9 +3875,6 @@
           <t>11-D-9004-01</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4330,9 +3892,6 @@
           <t>11-D-9146-01</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4350,9 +3909,6 @@
           <t>11-D-9156-01</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4370,9 +3926,6 @@
           <t>11-D-9156-04</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4390,9 +3943,6 @@
           <t>11-D-9297-01</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4410,9 +3960,6 @@
           <t>11-D-9298-01</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4430,9 +3977,6 @@
           <t>11-D-9443-01</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4450,9 +3994,6 @@
           <t>11-D-9534-01</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4470,9 +4011,6 @@
           <t>11-D-9535-01</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4490,9 +4028,6 @@
           <t>11-D-9539-01</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4510,9 +4045,6 @@
           <t>11-D-9643-01</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4530,9 +4062,6 @@
           <t>11-D-9643-02</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4550,9 +4079,6 @@
           <t>11-D-9732-01</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4570,9 +4096,6 @@
           <t>11-D-9733-01</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4590,9 +4113,6 @@
           <t>11-D-9736-02</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4610,9 +4130,6 @@
           <t>11-D-9740-01</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4630,9 +4147,6 @@
           <t>11-D-9741-01</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4650,9 +4164,6 @@
           <t>11-D-9742-01</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4670,9 +4181,6 @@
           <t>11-D-9775-01</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4690,9 +4198,6 @@
           <t>11-D-9812-01</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4710,9 +4215,6 @@
           <t>11-D-9814-01</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4730,9 +4232,6 @@
           <t>11-D-9817-01</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4750,9 +4249,6 @@
           <t>11-D-9819-01</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4770,9 +4266,6 @@
           <t>11-D-9820-01</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4790,9 +4283,6 @@
           <t>11-D-9821-01</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4810,9 +4300,6 @@
           <t>11-D-9824-01</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4830,9 +4317,6 @@
           <t>11-D-9825-01</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4850,9 +4334,6 @@
           <t>11-D-9828-01</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4870,9 +4351,6 @@
           <t>11-D-9829-01</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4890,9 +4368,6 @@
           <t>11-D-9832-01</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4910,9 +4385,6 @@
           <t>11-D-9903-01</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4930,9 +4402,6 @@
           <t>11-D-9978-201</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4950,9 +4419,6 @@
           <t>11-D-9978-202</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4970,9 +4436,6 @@
           <t>11-E-9246-01</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -4990,9 +4453,6 @@
           <t>11-E-9250-01</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5010,9 +4470,6 @@
           <t>11-E-9256-01</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5030,9 +4487,6 @@
           <t>11-E-9258-01</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5050,9 +4504,6 @@
           <t>11-E-9665-01</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5070,9 +4521,6 @@
           <t>11-E-9666-01</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5090,9 +4538,6 @@
           <t>11-E-9667-01</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5110,9 +4555,6 @@
           <t>11-E-9675-01</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5130,9 +4572,6 @@
           <t>11-E-9676-01</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5150,9 +4589,6 @@
           <t>11-E-9740-01</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5170,9 +4606,6 @@
           <t>11-E-9740-04</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5190,9 +4623,6 @@
           <t>11-E-9740-07</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5210,9 +4640,6 @@
           <t>11-E-9741-01</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5230,9 +4657,6 @@
           <t>11-E-9741-04</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5250,9 +4674,6 @@
           <t>11-E-9742-01</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5270,9 +4691,6 @@
           <t>11-E-9742-04</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5290,9 +4708,6 @@
           <t>11-E-9745-01</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5310,9 +4725,6 @@
           <t>11-E-9745-04</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5330,9 +4742,6 @@
           <t>11-E-9745-07</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5350,9 +4759,6 @@
           <t>11-E-9746-01</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5370,9 +4776,6 @@
           <t>11-E-9749-01</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5390,9 +4793,6 @@
           <t>11-E-9752-01</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5410,9 +4810,6 @@
           <t>11-E-9754-01</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5430,9 +4827,6 @@
           <t>11-E-9755-01</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5450,9 +4844,6 @@
           <t>11-E-9756-01</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5470,9 +4861,6 @@
           <t>11-E-9757-01</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5490,9 +4878,6 @@
           <t>11-E-9758-01</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5510,9 +4895,6 @@
           <t>11-E-9759-01</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5530,9 +4912,6 @@
           <t>11-E-9760-01</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5550,9 +4929,6 @@
           <t>11-E-9761-01</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5570,9 +4946,6 @@
           <t>11-E-9762-01</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5590,9 +4963,6 @@
           <t>11-E-9763-01</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5610,9 +4980,6 @@
           <t>11-E-9764-01</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5630,9 +4997,6 @@
           <t>11-E-9767-01</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5650,9 +5014,6 @@
           <t>11-E-9768-01</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5670,9 +5031,6 @@
           <t>11-E-9769-01</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5690,9 +5048,6 @@
           <t>11-E-9772-01</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5710,9 +5065,6 @@
           <t>11-E-9773-01</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5730,9 +5082,6 @@
           <t>11-E-9774-01</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5750,9 +5099,6 @@
           <t>11-E-9839-01</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5770,9 +5116,6 @@
           <t>11-E-9839-04</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5790,9 +5133,6 @@
           <t>11-E-9846-01</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5810,9 +5150,6 @@
           <t>11-E-9851-01</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5830,9 +5167,6 @@
           <t>11-E-9851-02</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -5850,9 +5184,6 @@
           <t>11-E-9870-02</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5870,9 +5201,6 @@
           <t>11-E-9871-02</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5890,9 +5218,6 @@
           <t>11-E-9872-02</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5910,9 +5235,6 @@
           <t>11-E-9892-01</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5930,9 +5252,6 @@
           <t>11-E-9892-03</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5950,9 +5269,6 @@
           <t>11-E-9893-01</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5970,9 +5286,6 @@
           <t>11-E-9893-03</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -5990,9 +5303,6 @@
           <t>11-E-9894-01</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6010,9 +5320,6 @@
           <t>11-E-9894-03</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6030,9 +5337,6 @@
           <t>11-E-9894-09</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6050,9 +5354,6 @@
           <t>11-E-9895-01</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6070,9 +5371,6 @@
           <t>11-E-9896-01</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6090,9 +5388,6 @@
           <t>11-E-9897-01</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6110,9 +5405,6 @@
           <t>11-E-9897-03</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6130,9 +5422,6 @@
           <t>11-E-9898-01</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6150,9 +5439,6 @@
           <t>11-E-9898-03</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6170,9 +5456,6 @@
           <t>11-E-9899-01</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6190,9 +5473,6 @@
           <t>11-E-9900-01</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6210,9 +5490,6 @@
           <t>11-E-9900-03</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6230,9 +5507,6 @@
           <t>11-E-9900-09</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6250,9 +5524,6 @@
           <t>11-E-9901-01</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6270,9 +5541,6 @@
           <t>11-E-9902-01</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6290,9 +5558,6 @@
           <t>11-E-9903-01</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6310,9 +5575,6 @@
           <t>11-E-9909-02</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6330,9 +5592,6 @@
           <t>11-E-9910-02</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6350,9 +5609,6 @@
           <t>11-E-9911-02</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6370,9 +5626,6 @@
           <t>11-F-9005-01</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6390,9 +5643,6 @@
           <t>11-F-9006-01</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6410,9 +5660,6 @@
           <t>11-F-9276-01</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6590,9 +5837,6 @@
           <t>12-6010-08</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6674,9 +5918,6 @@
           <t>12-6010-12</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr"/>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6736,7 +5977,6 @@
           <t>14GA</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -6764,7 +6004,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -6846,9 +6085,6 @@
           <t>12-6355-38</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr"/>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -6876,7 +6112,6 @@
           <t>14GA</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -6899,8 +6134,6 @@
           <t>12-A-6199-01-(12gacr ANSI-61) - K48 - V3-R0</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7014,9 +6247,6 @@
           <t>12-A-6348-03</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7258,9 +6488,6 @@
           <t>12-D-6013-01</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7288,7 +6515,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -7316,7 +6542,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -7339,8 +6564,6 @@
           <t>12-D-6030-10 - PLATE TOP GALVANIZADO</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -7422,9 +6645,6 @@
           <t>12-D-6047-09</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7474,9 +6694,6 @@
           <t>12-D-6066-01</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7494,9 +6711,6 @@
           <t>12-D-6075-01</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7546,9 +6760,6 @@
           <t>12-D-6079-05</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7635,8 +6846,6 @@
           <t>12-D-6081-05-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7760,7 +6969,6 @@
           <t>16GACR</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7906,9 +7114,6 @@
           <t>12-D-6087-07</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7931,8 +7136,6 @@
           <t>12-D-6088-06-(16gacr ANSI-61) - K48 - V2-R0</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -7987,8 +7190,6 @@
           <t>12-D-6089-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8038,9 +7239,6 @@
           <t>12-D-6090-06</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8058,9 +7256,6 @@
           <t>12-D-6090-07</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8083,8 +7278,6 @@
           <t>12-D-6091-01-(16gacr ANSI-61) - K48 - V1-R0</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8230,9 +7423,6 @@
           <t>12-D-6099-01</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8538,9 +7728,6 @@
           <t>12-D-6107-02</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8600,7 +7787,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -8628,7 +7814,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -8710,13 +7895,11 @@
           <t>12-D-6412-01</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8734,13 +7917,11 @@
           <t>12-D-6412-03</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8758,13 +7939,11 @@
           <t>12-D-6412-05</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr">
         <is>
           <t>14GACR</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8883,8 +8062,6 @@
           <t>16-6082-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -8902,13 +8079,11 @@
           <t>16-A-6001-01</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
           <t>12GACR</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -9374,9 +8549,6 @@
           <t>P15324-19</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr"/>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -9394,9 +8566,6 @@
           <t>P15899-10</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr"/>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -9424,7 +8593,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -9932,7 +9100,6 @@
           <t>14GA</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10024,7 +9191,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10052,7 +9218,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10080,7 +9245,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10268,7 +9432,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10328,7 +9491,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10356,7 +9518,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10384,7 +9545,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10412,7 +9572,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10440,7 +9599,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10458,9 +9616,6 @@
           <t>P20553-09</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10478,9 +9633,6 @@
           <t>P20557-20</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10498,9 +9650,6 @@
           <t>P20557-21</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10518,9 +9667,6 @@
           <t>P20593-15</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr"/>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10538,9 +9684,6 @@
           <t>P20596-21</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr"/>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10558,9 +9701,6 @@
           <t>P20596-22</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr"/>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10610,9 +9750,6 @@
           <t>P8815-03</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10630,9 +9767,6 @@
           <t>P8815-04</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10650,9 +9784,6 @@
           <t>P9711-08</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10670,9 +9801,6 @@
           <t>P9711-081</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10690,9 +9818,6 @@
           <t>PP10218-13</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10816,7 +9941,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10844,7 +9968,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10872,7 +9995,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10900,7 +10022,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -10923,8 +10044,6 @@
           <t>PP14023-01-(16gacr ANSI-61) - K48 - V0-R0</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -10984,7 +10103,6 @@
           <t>10GA</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11034,9 +10152,6 @@
           <t>PP14873-01</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr"/>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11054,9 +10169,6 @@
           <t>PP14873-02</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr"/>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11298,9 +10410,6 @@
           <t>PP19187-05</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr"/>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11392,7 +10501,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11420,7 +10528,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11448,7 +10555,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11476,7 +10582,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11504,7 +10609,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11532,7 +10636,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11560,7 +10663,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11588,7 +10690,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11616,7 +10717,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11644,7 +10744,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -11662,9 +10761,6 @@
           <t>PP20825-02</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr"/>
-      <c r="C466" t="inlineStr"/>
-      <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11682,9 +10778,6 @@
           <t>PP21139-081</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr"/>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11702,9 +10795,6 @@
           <t>PP21139-082</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr"/>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11722,9 +10812,6 @@
           <t>PP21139-091</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -11742,9 +10829,6 @@
           <t>PP21139-092</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr"/>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12082,9 +11166,6 @@
           <t>PP6868-113</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr"/>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12102,9 +11183,6 @@
           <t>PP7114-72</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr"/>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12218,9 +11296,6 @@
           <t>PP8192-05</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr"/>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12238,10 +11313,6 @@
           <t>11-D-6195-05</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr"/>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
           <t>SWB00084</t>
@@ -12254,10 +11325,6 @@
           <t>11-D-6195-06</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr"/>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
           <t>SWB01454</t>
@@ -12270,10 +11337,6 @@
           <t>P9014-102</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr"/>
-      <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
-      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
           <t>SWB01512</t>
@@ -12520,7 +11583,6 @@
           <t>12GA</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12735,8 +11797,6 @@
           <t>12-D-6083-03</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12759,8 +11819,6 @@
           <t>12-D-6106-01</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12783,8 +11841,6 @@
           <t>PP21139-092 TRTO - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12807,8 +11863,6 @@
           <t>PP21139-092 TRT0 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12831,8 +11885,6 @@
           <t>P9711-081 TRTO 2 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12855,8 +11907,6 @@
           <t>P9711-081 TRT0 2 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12879,8 +11929,6 @@
           <t>P7911-081 TRTO 1 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12903,8 +11951,6 @@
           <t>P7911-081 TRT0 1 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12927,8 +11973,6 @@
           <t>P9711-081 TRTO 1 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr"/>
-      <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -12951,8 +11995,6 @@
           <t>P9711-081 TRT0 1 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13135,8 +12177,6 @@
           <t>P9711-081 TRTO - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13159,8 +12199,6 @@
           <t>P9711-081 TRT0 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13183,8 +12221,6 @@
           <t>PP21139-081 TRTO - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13207,8 +12243,6 @@
           <t>PP21139-081 TRT0 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13231,8 +12265,6 @@
           <t>11-C-9778-01 TRTO - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13255,8 +12287,6 @@
           <t>11-C-9778-01 TRT0 - Proyecto TORONTO</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr"/>
-      <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13279,8 +12309,16 @@
           <t>12-D-6030-07 - PLATE TOP GALVANIZADO</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -13303,8 +12341,16 @@
           <t>12-D-6030-08 - PLATE TOP GALVANIZADO</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>Galvanizado</t>
@@ -13319,16 +12365,19 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>11-A-9581-01 TRTO</t>
+          <t>11-A-9581-01 TRTC</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>11-A-9581-01 TRTO</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr"/>
-      <c r="D527" t="inlineStr"/>
+          <t>11-A-9581-01 TRTC - RUN-BACK LUG BRACKET (TORONTO)</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Decapado CAL 16 (16 GA)</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>Ansi 61</t>
@@ -13336,35 +12385,175 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>11-A-9581-01 TRTO</t>
+          <t>ISSIV00746</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
+          <t>11-A-9581-01 TRTO</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>11-A-9581-01 TRTO - RUN-BACK LUG BRACKET (TORONTO)</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Decapado CAL 16 (16 GA)</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>ISSIV00746</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>11-A-9581-01 TRT0</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>11-A-9581-01 TRT0 - RUN-BACK LUG BRACKET (TORONTO)</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Decapado CAL 16 (16 GA)</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>ISSIV00746</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRTC</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRTC - Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Galvanizado</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>11-E-9770-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRTO</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRTO - Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Galvanizado</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>11-E-9770-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRT0</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRT0 - Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Galvanizado</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>11-E-9770-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>11-E-9770-02</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 - Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Galvanizado</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>11-E-9770-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
           <t>12-D-6091-07</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B534" t="inlineStr">
         <is>
           <t>12-D-6091-07</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>Ansi 61</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Ansi 61</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
         <is>
           <t>12-D-6091-07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>